--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.19874833921648</v>
+        <v>1.819796605122678</v>
       </c>
       <c r="D2" t="n">
-        <v>10.95730564381747</v>
+        <v>1.780562167120339</v>
       </c>
       <c r="E2" t="n">
-        <v>25.21898269357067</v>
+        <v>4.098084687705235</v>
       </c>
       <c r="F2" t="n">
-        <v>25.23029085332485</v>
+        <v>4.099922263665289</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.63671372635783</v>
+        <v>10.01596598053315</v>
       </c>
       <c r="D3" t="n">
-        <v>61.41788735046718</v>
+        <v>9.980406694450917</v>
       </c>
       <c r="E3" t="n">
-        <v>25.21898269357067</v>
+        <v>4.098084687705235</v>
       </c>
       <c r="F3" t="n">
-        <v>25.23029085332485</v>
+        <v>4.099922263665289</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
